--- a/scholarship_application_forms/042_culinary_scholarship_application_submission_form--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/042_culinary_scholarship_application_submission_form--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'culinary_arts'}</t>
+          <t>culinary_arts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Culinary Arts'}</t>
+          <t>Culinary Arts</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'hospitality_management'}</t>
+          <t>hospitality_management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Hospitality Management'}</t>
+          <t>Hospitality Management</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'merit-based_scholarship'}</t>
+          <t>merit-based_scholarship</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Merit-based Scholarship'}</t>
+          <t>Merit-based Scholarship</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'needs-based_scholarship'}</t>
+          <t>needs-based_scholarship</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Needs-based Scholarship'}</t>
+          <t>Needs-based Scholarship</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'withdrawn'}</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Withdrawn'}</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Recurring'}</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'semesterly'}</t>
+          <t>semesterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Semesterly'}</t>
+          <t>Semesterly</t>
         </is>
       </c>
     </row>
